--- a/Bhojpatra_Progress_Tracker.xlsx
+++ b/Bhojpatra_Progress_Tracker.xlsx
@@ -1496,10 +1496,10 @@
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="17" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E56" s="9"/>
     </row>
@@ -1509,10 +1509,10 @@
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="17" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E57" s="9"/>
     </row>

--- a/Bhojpatra_Progress_Tracker.xlsx
+++ b/Bhojpatra_Progress_Tracker.xlsx
@@ -1340,10 +1340,10 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="17" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E44" s="9"/>
     </row>
